--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/GEORGIA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/GEORGIA_2012.xlsx
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C174">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C204">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C732">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C830">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C872">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C880">
@@ -23154,7 +23154,7 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1267">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="B1293" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1293">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1443">
